--- a/data/out/variants/v8_only_gen_no_solar_enso_lags/raw_v8_only_gen_no_solar_enso_lags.xlsx
+++ b/data/out/variants/v8_only_gen_no_solar_enso_lags/raw_v8_only_gen_no_solar_enso_lags.xlsx
@@ -550,7 +550,7 @@
         <v>9639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02477359771728516</v>
+        <v>0.03702282905578613</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -604,7 +604,7 @@
         <v>9639</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02029514312744141</v>
+        <v>0.02817630767822266</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>9639</v>
       </c>
       <c r="N4" t="n">
-        <v>0.04203701019287109</v>
+        <v>0.06599545478820801</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         <v>9639</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4464242458343506</v>
+        <v>1.693909406661987</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>9639</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8047566413879395</v>
+        <v>3.608075857162476</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>9639</v>
       </c>
       <c r="N7" t="n">
-        <v>240.4867770671844</v>
+        <v>728.1240985393524</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>9639</v>
       </c>
       <c r="N8" t="n">
-        <v>155.516978263855</v>
+        <v>367.8532917499542</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         <v>9639</v>
       </c>
       <c r="N9" t="n">
-        <v>99.21679425239563</v>
+        <v>216.5440530776978</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>9639</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5525178909301758</v>
+        <v>0.8876302242279053</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1048,23 +1048,23 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 839, 'learning_rate': 0.08500859594031757, 'max_depth': 4, 'subsample': 0.6428326867556541, 'colsample_bytree': 0.92453067438032}</t>
+          <t>{'n_estimators': 348, 'learning_rate': 0.05080599114588148, 'max_depth': 4, 'subsample': 0.9239328422852651, 'colsample_bytree': 0.9668511548993652}</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.2402971134153846</v>
+        <v>0.2632881886259996</v>
       </c>
       <c r="G11" t="n">
-        <v>244.5090493664394</v>
+        <v>236.5284364205662</v>
       </c>
       <c r="H11" t="n">
-        <v>190907.0785446385</v>
+        <v>185129.6106969239</v>
       </c>
       <c r="I11" t="n">
-        <v>436.9291459088516</v>
+        <v>430.2669063464258</v>
       </c>
       <c r="J11" t="n">
-        <v>49.52339157481369</v>
+        <v>45.68994603969143</v>
       </c>
       <c r="K11" t="n">
         <v>48192</v>
@@ -1076,7 +1076,7 @@
         <v>9639</v>
       </c>
       <c r="N11" t="n">
-        <v>53.70723628997803</v>
+        <v>72.66358160972595</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1106,23 +1106,23 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 665, 'learning_rate': 0.01681162561821809, 'num_leaves': 122, 'min_child_samples': 48}</t>
+          <t>{'n_estimators': 517, 'learning_rate': 0.016804996063056042, 'num_leaves': 59, 'min_child_samples': 46}</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.1753718006658338</v>
+        <v>0.1958593276714543</v>
       </c>
       <c r="G12" t="n">
-        <v>250.419375183715</v>
+        <v>245.4454340474359</v>
       </c>
       <c r="H12" t="n">
-        <v>207222.2749187584</v>
+        <v>202073.92811593</v>
       </c>
       <c r="I12" t="n">
-        <v>455.2167340056365</v>
+        <v>449.5263375108627</v>
       </c>
       <c r="J12" t="n">
-        <v>50.3948906235846</v>
+        <v>48.44582119506518</v>
       </c>
       <c r="K12" t="n">
         <v>48192</v>
@@ -1134,7 +1134,7 @@
         <v>9639</v>
       </c>
       <c r="N12" t="n">
-        <v>165.1828632354736</v>
+        <v>260.6684248447418</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1164,23 +1164,23 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>{'iterations': 806, 'learning_rate': 0.04820512450871174, 'depth': 4}</t>
+          <t>{'iterations': 746, 'learning_rate': 0.09922271134678981, 'depth': 4}</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.1868996823326329</v>
+        <v>0.2098804464244168</v>
       </c>
       <c r="G13" t="n">
-        <v>250.5751840225284</v>
+        <v>245.2363578835614</v>
       </c>
       <c r="H13" t="n">
-        <v>204325.4131986314</v>
+        <v>198550.5364501575</v>
       </c>
       <c r="I13" t="n">
-        <v>452.0236865459945</v>
+        <v>445.590099138387</v>
       </c>
       <c r="J13" t="n">
-        <v>48.49347940795715</v>
+        <v>47.43512695487082</v>
       </c>
       <c r="K13" t="n">
         <v>48192</v>
@@ -1192,7 +1192,7 @@
         <v>9639</v>
       </c>
       <c r="N13" t="n">
-        <v>93.51869487762451</v>
+        <v>261.3344895839691</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>448.7673378532652</v>
       </c>
       <c r="J14" t="n">
-        <v>55.47155285712876</v>
+        <v>55.47155285712875</v>
       </c>
       <c r="K14" t="n">
         <v>48192</v>
@@ -1250,7 +1250,7 @@
         <v>9639</v>
       </c>
       <c r="N14" t="n">
-        <v>34.67983150482178</v>
+        <v>118.1613855361938</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>9639</v>
       </c>
       <c r="N15" t="n">
-        <v>7.598451852798462</v>
+        <v>22.85760688781738</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>9639</v>
       </c>
       <c r="N16" t="n">
-        <v>561.6939356327057</v>
+        <v>1480.241189718246</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
